--- a/data/5_interpretation_Paolo_complete.xlsx
+++ b/data/5_interpretation_Paolo_complete.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ausport.sharepoint.com/sites/PerformanceScience/Shared Documents/General/Research/AIS Research - statistics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\HCUAVG9115\R_AIS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{F1BB86D2-4669-41D8-BC6D-85F80FD147C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B26D2969-BE81-4755-B97E-48AE1626B1EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA92068A-4FE7-43F5-901E-EA9DB1A2C667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interpretations" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="358">
   <si>
     <t>doi</t>
   </si>
@@ -1070,9 +1070,6 @@
     <t>answer: TRUE overinterpreted, FALSE not overinterpreted, NA</t>
   </si>
   <si>
-    <t>COI, I'm an author</t>
-  </si>
-  <si>
     <t>conclusions seem to be reasonable, but the commentary is not a direct consequence of the study. It feels like a stretch, to increase relevance of study</t>
   </si>
   <si>
@@ -1104,6 +1101,14 @@
   </si>
   <si>
     <t>"nonetheless, the consumption of pp fruit juice may increase awareness of its putative health benefits and may promote consumption of the whole frui"</t>
+  </si>
+  <si>
+    <t>COI, I'm an author
+Assessed by Adrian. Judged as a measured set of recommendations.</t>
+  </si>
+  <si>
+    <t>COI, I'm an author. 
+Assessed by Adrian. Small sample size and language was relatively strong, but wasn't overly strong and did note some caution.</t>
   </si>
 </sst>
 </file>
@@ -1207,10 +1212,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1526,7 +1527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1593,7 +1594,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -1764,11 +1765,11 @@
       <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
+      <c r="F12" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -1791,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -2375,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="145" x14ac:dyDescent="0.35">
@@ -2482,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -2593,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -3142,7 +3143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>228</v>
       </c>
@@ -3158,11 +3159,11 @@
       <c r="E74" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>10</v>
+      <c r="F74" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -3208,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -3317,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -3455,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="116" x14ac:dyDescent="0.35">
@@ -3520,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -3585,7 +3586,7 @@
         <v>1</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="145" x14ac:dyDescent="0.35">
@@ -3675,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
@@ -3763,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
@@ -5073,15 +5074,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="15a7796b-2524-4707-811a-e9b851f49def" xsi:nil="true"/>
@@ -5090,6 +5082,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5112,14 +5113,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFBCD1-8E46-4709-8454-C421F828A812}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{209072DC-0C52-41AF-86CC-732A8789E788}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5128,4 +5121,12 @@
     <ds:schemaRef ds:uri="42c9f3dc-5c27-449d-adef-abeb255b72d0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFBCD1-8E46-4709-8454-C421F828A812}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>